--- a/campuso-ders-programi-2026-2027-guz.xlsx
+++ b/campuso-ders-programi-2026-2027-guz.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2064,7 +2064,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3615,7 +3615,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3756,7 +3756,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4555,7 +4555,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5166,7 +5166,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bankacılık ve Finans</t>
+          <t>Finans ve Bankacılık</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
